--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\All Auto Post\History - Sanu Old\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57DEB851-13CA-46AD-960E-F60D46997AB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDE81B19-C371-4326-881F-5F66F2642570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CEBFA179-F109-4830-AF10-F3EF48EB9847}"/>
   </bookViews>
@@ -564,7 +564,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="4">
-        <v>46250.754166666666</v>
+        <v>46250.759027777778</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>8</v>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\All Auto Post\History - Sanu Old\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDE81B19-C371-4326-881F-5F66F2642570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C9306A1-1554-40BC-AFA3-148F5BC86E98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CEBFA179-F109-4830-AF10-F3EF48EB9847}"/>
   </bookViews>
@@ -564,7 +564,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="4">
-        <v>46250.759027777778</v>
+        <v>46250.763888888891</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>8</v>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\All Auto Post\History - Sanu Old\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C9306A1-1554-40BC-AFA3-148F5BC86E98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D754A28-778F-4556-A300-DF6131C3070A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CEBFA179-F109-4830-AF10-F3EF48EB9847}"/>
   </bookViews>
@@ -564,7 +564,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="4">
-        <v>46250.763888888891</v>
+        <v>46250.774305555555</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>8</v>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\All Auto Post\History - Sanu Old\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D754A28-778F-4556-A300-DF6131C3070A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB0D6E6-40A4-47C9-B38B-8FA02B4BFE9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CEBFA179-F109-4830-AF10-F3EF48EB9847}"/>
   </bookViews>
@@ -564,7 +564,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="4">
-        <v>46250.774305555555</v>
+        <v>46250.77847222222</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>8</v>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -642,9 +642,14 @@
       <c r="E2" s="12" t="n">
         <v>46258.14861111111</v>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F2" s="16" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>4094618310844746</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -675,9 +675,14 @@
       <c r="E3" s="12" t="n">
         <v>46258.23472222222</v>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1541117730544247</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -708,9 +708,14 @@
       <c r="E4" s="12" t="n">
         <v>46258.90416666667</v>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1808680926793619</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -741,9 +741,14 @@
       <c r="E5" s="12" t="n">
         <v>46259.14861111111</v>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1870872710987957</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -774,9 +774,14 @@
       <c r="E6" s="12" t="n">
         <v>46259.23472222222</v>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2086210725318426</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -821,9 +821,14 @@
       <c r="E7" s="12" t="n">
         <v>46259.90416666667</v>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2614302142347496</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -854,9 +854,14 @@
       <c r="E8" s="12" t="n">
         <v>46260.14861111111</v>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1347304117146761</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6483,9 +6483,14 @@
       <c r="E208" s="12" t="n">
         <v>46260.19444444445</v>
       </c>
-      <c r="F208" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F208" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>1032710689608614</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -887,9 +887,14 @@
       <c r="E9" s="12" t="n">
         <v>46260.23472222222</v>
       </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1218445700458512</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1018,9 +1018,14 @@
       <c r="E13" s="12" t="n">
         <v>46261.90416666667</v>
       </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>914322268417549</t>
         </is>
       </c>
     </row>
@@ -6620,9 +6625,14 @@
       <c r="E212" s="12" t="n">
         <v>46261.67152777778</v>
       </c>
-      <c r="F212" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F212" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>1034121946134155</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6658,9 +6658,14 @@
       <c r="E213" s="12" t="n">
         <v>46261.98333333333</v>
       </c>
-      <c r="F213" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F213" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>1034181856128164</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1051,9 +1051,14 @@
       <c r="E14" s="12" t="n">
         <v>46262.14861111111</v>
       </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>4533500573630871</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6696,9 +6696,14 @@
       <c r="E214" s="12" t="n">
         <v>46262.19444444445</v>
       </c>
-      <c r="F214" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F214" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>1034337766112573</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1084,9 +1084,14 @@
       <c r="E15" s="12" t="n">
         <v>46262.23472222222</v>
       </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1745039899936840</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6734,9 +6734,14 @@
       <c r="E215" s="12" t="n">
         <v>46262.67152777778</v>
       </c>
-      <c r="F215" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F215" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>1034740339405649</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1117,9 +1117,14 @@
       <c r="E16" s="12" t="n">
         <v>46262.90416666667</v>
       </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1748498539527482</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6772,9 +6772,14 @@
       <c r="E216" s="12" t="n">
         <v>46262.98333333333</v>
       </c>
-      <c r="F216" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F216" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>1035049122708104</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1150,9 +1150,14 @@
       <c r="E17" s="12" t="n">
         <v>46263.14861111111</v>
       </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1090382347269245</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6810,9 +6810,14 @@
       <c r="E217" s="12" t="n">
         <v>46263.19444444445</v>
       </c>
-      <c r="F217" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F217" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>1035198596026490</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1183,9 +1183,14 @@
       <c r="E18" s="12" t="n">
         <v>46263.23472222222</v>
       </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2331622064242149</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6848,9 +6848,14 @@
       <c r="E218" s="12" t="n">
         <v>46263.67152777778</v>
       </c>
-      <c r="F218" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F218" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>1035565745989775</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1216,9 +1216,14 @@
       <c r="E19" s="12" t="n">
         <v>46263.90416666667</v>
       </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1624030692717937</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6886,9 +6886,14 @@
       <c r="E219" s="12" t="n">
         <v>46263.98333333333</v>
       </c>
-      <c r="F219" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F219" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>1035862052626811</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1249,9 +1249,14 @@
       <c r="E20" s="12" t="n">
         <v>46264.14861111111</v>
       </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F20" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1652497349572171</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6924,9 +6924,14 @@
       <c r="E220" s="12" t="n">
         <v>46264.19444444445</v>
       </c>
-      <c r="F220" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F220" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>1036013839278299</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1282,9 +1282,14 @@
       <c r="E21" s="12" t="n">
         <v>46264.23472222222</v>
       </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1640430887640975</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6962,9 +6962,14 @@
       <c r="E221" s="12" t="n">
         <v>46264.67152777778</v>
       </c>
-      <c r="F221" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F221" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>1036385819241101</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1315,9 +1315,14 @@
       <c r="E22" s="12" t="n">
         <v>46264.90416666667</v>
       </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F22" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2564353320751805</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7000,9 +7000,14 @@
       <c r="E222" s="12" t="n">
         <v>46264.98333333333</v>
       </c>
-      <c r="F222" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F222" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>1036684709211212</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1348,9 +1348,14 @@
       <c r="E23" s="12" t="n">
         <v>46265.14861111111</v>
       </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F23" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1078129008077624</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7038,9 +7038,14 @@
       <c r="E223" s="12" t="n">
         <v>46265.19444444445</v>
       </c>
-      <c r="F223" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F223" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>1036837232529293</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1381,9 +1381,14 @@
       <c r="E24" s="12" t="n">
         <v>46265.23472222222</v>
       </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F24" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2536977616768484</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7076,9 +7076,14 @@
       <c r="E224" s="12" t="n">
         <v>46265.67152777778</v>
       </c>
-      <c r="F224" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F224" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>1037199942493022</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1414,9 +1414,14 @@
       <c r="E25" s="12" t="n">
         <v>46265.90416666667</v>
       </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F25" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1085249577282895</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7114,9 +7114,14 @@
       <c r="E225" s="12" t="n">
         <v>46265.98333333333</v>
       </c>
-      <c r="F225" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F225" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>1037490355797314</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1447,9 +1447,14 @@
       <c r="E26" s="12" t="n">
         <v>46266.14861111111</v>
       </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F26" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1276552171169140</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7152,9 +7152,14 @@
       <c r="E226" s="12" t="n">
         <v>46266.19444444445</v>
       </c>
-      <c r="F226" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F226" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>1037643449115338</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1480,9 +1480,14 @@
       <c r="E27" s="12" t="n">
         <v>46266.23472222222</v>
       </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F27" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>922504164262531</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7190,9 +7190,14 @@
       <c r="E227" s="12" t="n">
         <v>46266.67152777778</v>
       </c>
-      <c r="F227" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F227" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>1038017692411247</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1513,9 +1513,14 @@
       <c r="E28" s="12" t="n">
         <v>46266.90416666667</v>
       </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F28" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1089483324024754</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7228,9 +7228,14 @@
       <c r="E228" s="12" t="n">
         <v>46266.98333333333</v>
       </c>
-      <c r="F228" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F228" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>1038323389047344</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1546,9 +1546,14 @@
       <c r="E29" s="12" t="n">
         <v>46267.14861111111</v>
       </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F29" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2588795734912424</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7266,9 +7266,14 @@
       <c r="E229" s="12" t="n">
         <v>46267.19444444445</v>
       </c>
-      <c r="F229" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F229" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>1038480529031630</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1579,9 +1579,14 @@
       <c r="E30" s="12" t="n">
         <v>46267.23472222222</v>
       </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F30" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1570315924471244</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7304,9 +7304,14 @@
       <c r="E230" s="12" t="n">
         <v>46267.67152777778</v>
       </c>
-      <c r="F230" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F230" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>1038856008994082</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1612,9 +1612,14 @@
       <c r="E31" s="12" t="n">
         <v>46267.90416666667</v>
       </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F31" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1600002214953392</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7342,9 +7342,14 @@
       <c r="E231" s="12" t="n">
         <v>46267.98333333333</v>
       </c>
-      <c r="F231" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F231" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>1039159552297061</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1645,9 +1645,14 @@
       <c r="E32" s="12" t="n">
         <v>46268.14861111111</v>
       </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F32" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1430745535537721</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7380,9 +7380,14 @@
       <c r="E232" s="12" t="n">
         <v>46268.19444444445</v>
       </c>
-      <c r="F232" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F232" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>1039312672281749</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1678,9 +1678,14 @@
       <c r="E33" s="12" t="n">
         <v>46268.23472222222</v>
       </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F33" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1081207098014647</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7418,9 +7418,14 @@
       <c r="E233" s="12" t="n">
         <v>46268.67152777778</v>
       </c>
-      <c r="F233" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F233" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>1039683155578034</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1711,9 +1711,14 @@
       <c r="E34" s="12" t="n">
         <v>46268.90416666667</v>
       </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F34" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2835872390111881</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7456,9 +7456,14 @@
       <c r="E234" s="12" t="n">
         <v>46268.98333333333</v>
       </c>
-      <c r="F234" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F234" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>1039980825548267</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1744,9 +1744,14 @@
       <c r="E35" s="12" t="n">
         <v>46269.14861111111</v>
       </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F35" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>904291479142509</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7494,9 +7494,14 @@
       <c r="E235" s="12" t="n">
         <v>46269.19444444445</v>
       </c>
-      <c r="F235" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F235" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>1040140745532275</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1777,9 +1777,14 @@
       <c r="E36" s="12" t="n">
         <v>46269.23472222222</v>
       </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F36" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1317750943576837</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7532,9 +7532,14 @@
       <c r="E236" s="12" t="n">
         <v>46269.67152777778</v>
       </c>
-      <c r="F236" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F236" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>1040534998826183</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1810,9 +1810,14 @@
       <c r="E37" s="12" t="n">
         <v>46269.90416666667</v>
       </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F37" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2465466737296696</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7570,9 +7570,14 @@
       <c r="E237" s="12" t="n">
         <v>46269.98333333333</v>
       </c>
-      <c r="F237" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F237" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>1040845412128475</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1843,9 +1843,14 @@
       <c r="E38" s="12" t="n">
         <v>46270.14861111111</v>
       </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F38" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1098946969150727</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7608,9 +7608,14 @@
       <c r="E238" s="12" t="n">
         <v>46270.19444444445</v>
       </c>
-      <c r="F238" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F238" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>1041019932111023</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1876,9 +1876,14 @@
       <c r="E39" s="12" t="n">
         <v>46270.23472222222</v>
       </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F39" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1420527230045366</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7646,9 +7646,14 @@
       <c r="E239" s="12" t="n">
         <v>46270.67152777778</v>
       </c>
-      <c r="F239" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F239" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>1041405215405828</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1909,9 +1909,14 @@
       <c r="E40" s="12" t="n">
         <v>46270.90416666667</v>
       </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F40" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2508570799668724</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7684,9 +7684,14 @@
       <c r="E240" s="12" t="n">
         <v>46270.98333333333</v>
       </c>
-      <c r="F240" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F240" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>1041707672042249</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1942,9 +1942,14 @@
       <c r="E41" s="12" t="n">
         <v>46271.14861111111</v>
       </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F41" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1867675724643041</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7722,9 +7722,14 @@
       <c r="E241" s="12" t="n">
         <v>46271.19444444445</v>
       </c>
-      <c r="F241" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F241" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>1041854902027526</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1975,9 +1975,14 @@
       <c r="E42" s="12" t="n">
         <v>46271.23472222222</v>
       </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F42" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1583617816880316</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7760,9 +7760,14 @@
       <c r="E242" s="12" t="n">
         <v>46271.67152777778</v>
       </c>
-      <c r="F242" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F242" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>1042240558655627</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2008,9 +2008,14 @@
       <c r="E43" s="12" t="n">
         <v>46271.90416666667</v>
       </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F43" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2023793744985906</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7798,9 +7798,14 @@
       <c r="E243" s="12" t="n">
         <v>46271.98333333333</v>
       </c>
-      <c r="F243" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F243" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>1042541865292163</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2041,9 +2041,14 @@
       <c r="E44" s="12" t="n">
         <v>46272.14861111111</v>
       </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F44" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1558962588845244</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7836,9 +7836,14 @@
       <c r="E244" s="12" t="n">
         <v>46272.19444444445</v>
       </c>
-      <c r="F244" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F244" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>1042692865277063</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2074,9 +2074,14 @@
       <c r="E45" s="12" t="n">
         <v>46272.23472222222</v>
       </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F45" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1754149609242708</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7874,9 +7874,14 @@
       <c r="E245" s="12" t="n">
         <v>46272.67152777778</v>
       </c>
-      <c r="F245" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F245" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>1043055285240821</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2107,9 +2107,14 @@
       <c r="E46" s="12" t="n">
         <v>46272.90416666667</v>
       </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F46" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1116153640746284</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7912,9 +7912,14 @@
       <c r="E246" s="12" t="n">
         <v>46272.98333333333</v>
       </c>
-      <c r="F246" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F246" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>1043356691877347</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2140,9 +2140,14 @@
       <c r="E47" s="12" t="n">
         <v>46273.14861111111</v>
       </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F47" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1055515627254889</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7950,9 +7950,14 @@
       <c r="E247" s="12" t="n">
         <v>46273.19444444445</v>
       </c>
-      <c r="F247" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F247" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>1043521321860884</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2173,9 +2173,14 @@
       <c r="E48" s="12" t="n">
         <v>46273.23472222222</v>
       </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F48" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1059981870231800</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7988,9 +7988,14 @@
       <c r="E248" s="12" t="n">
         <v>46273.67152777778</v>
       </c>
-      <c r="F248" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F248" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>1043898518489831</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2206,9 +2206,14 @@
       <c r="E49" s="12" t="n">
         <v>46273.90416666667</v>
       </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F49" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>835542899585245</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8026,9 +8026,14 @@
       <c r="E249" s="12" t="n">
         <v>46273.98333333333</v>
       </c>
-      <c r="F249" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F249" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>1044209305125419</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2239,9 +2239,14 @@
       <c r="E50" s="12" t="n">
         <v>46274.14861111111</v>
       </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F50" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2628816460909630</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8064,9 +8064,14 @@
       <c r="E250" s="12" t="n">
         <v>46274.19444444445</v>
       </c>
-      <c r="F250" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F250" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>1044369521776064</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2272,9 +2272,14 @@
       <c r="E51" s="12" t="n">
         <v>46274.23472222222</v>
       </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F51" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1054849460779779</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8102,9 +8102,14 @@
       <c r="E251" s="12" t="n">
         <v>46274.67152777778</v>
       </c>
-      <c r="F251" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F251" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>1044743985071951</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2305,9 +2305,14 @@
       <c r="E52" s="12" t="n">
         <v>46274.90416666667</v>
       </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F52" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1589587879229102</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8140,9 +8140,14 @@
       <c r="E252" s="12" t="n">
         <v>46274.98333333333</v>
       </c>
-      <c r="F252" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F252" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>1045048768374806</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2338,9 +2338,14 @@
       <c r="E53" s="12" t="n">
         <v>46275.14861111111</v>
       </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F53" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1805312854124547</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8178,9 +8178,14 @@
       <c r="E253" s="12" t="n">
         <v>46275.19444444445</v>
       </c>
-      <c r="F253" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F253" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>1045210411691975</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2371,9 +2371,14 @@
       <c r="E54" s="12" t="n">
         <v>46275.23472222222</v>
       </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F54" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1856847008809340</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8216,9 +8216,14 @@
       <c r="E254" s="12" t="n">
         <v>46275.67152777778</v>
       </c>
-      <c r="F254" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F254" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>1045590954987254</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2404,9 +2404,14 @@
       <c r="E55" s="12" t="n">
         <v>46275.90416666667</v>
       </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F55" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1091163103400461</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8254,9 +8254,14 @@
       <c r="E255" s="12" t="n">
         <v>46275.98333333333</v>
       </c>
-      <c r="F255" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F255" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>1045897654956584</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2437,9 +2437,14 @@
       <c r="E56" s="12" t="n">
         <v>46276.14861111111</v>
       </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F56" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1374225144859826</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8292,9 +8292,14 @@
       <c r="E256" s="12" t="n">
         <v>46276.19444444445</v>
       </c>
-      <c r="F256" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F256" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>1046063024940047</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2470,9 +2470,14 @@
       <c r="E57" s="12" t="n">
         <v>46276.23472222222</v>
       </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F57" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1147595837914017</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8330,9 +8330,14 @@
       <c r="E257" s="12" t="n">
         <v>46276.67152777778</v>
       </c>
-      <c r="F257" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F257" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>1046434034902946</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2503,9 +2503,14 @@
       <c r="E58" s="12" t="n">
         <v>46276.90416666667</v>
       </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F58" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1086311353763149</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8368,9 +8368,14 @@
       <c r="E258" s="12" t="n">
         <v>46276.98333333333</v>
       </c>
-      <c r="F258" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F258" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>1046748954871454</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2536,9 +2536,14 @@
       <c r="E59" s="12" t="n">
         <v>46277.14861111111</v>
       </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F59" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2687246678386693</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8406,9 +8406,14 @@
       <c r="E259" s="12" t="n">
         <v>46277.19444444445</v>
       </c>
-      <c r="F259" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F259" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>1046907818188901</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2569,9 +2569,14 @@
       <c r="E60" s="12" t="n">
         <v>46277.23472222222</v>
       </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F60" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1079010644992709</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8444,9 +8444,14 @@
       <c r="E260" s="12" t="n">
         <v>46277.67152777778</v>
       </c>
-      <c r="F260" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F260" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>1047278731485143</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2602,9 +2602,14 @@
       <c r="E61" s="12" t="n">
         <v>46277.90416666667</v>
       </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F61" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1102824179095159</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8482,9 +8482,14 @@
       <c r="E261" s="12" t="n">
         <v>46277.98333333333</v>
       </c>
-      <c r="F261" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F261" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>1047584541454562</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2635,9 +2635,14 @@
       <c r="E62" s="12" t="n">
         <v>46278.14861111111</v>
       </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F62" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1390129913333766</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8520,9 +8520,14 @@
       <c r="E262" s="12" t="n">
         <v>46278.19444444445</v>
       </c>
-      <c r="F262" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F262" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>1047734254772924</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2668,9 +2668,14 @@
       <c r="E63" s="12" t="n">
         <v>46278.23472222222</v>
       </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F63" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2104094360198670</t>
         </is>
       </c>
     </row>
